--- a/연구코드/results/regression/cross_hospital_summary.xlsx
+++ b/연구코드/results/regression/cross_hospital_summary.xlsx
@@ -1,37 +1,114 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="23">
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <t>N_features</t>
+  </si>
+  <si>
+    <t>N_rows</t>
+  </si>
+  <si>
+    <t>Lin_R2</t>
+  </si>
+  <si>
+    <t>Lin_R2_std</t>
+  </si>
+  <si>
+    <t>Lin_MAE</t>
+  </si>
+  <si>
+    <t>Lin_RMSE</t>
+  </si>
+  <si>
+    <t>TAMA_threshold</t>
+  </si>
+  <si>
+    <t>Log_AUC</t>
+  </si>
+  <si>
+    <t>Log_AUC_std</t>
+  </si>
+  <si>
+    <t>Log_Acc</t>
+  </si>
+  <si>
+    <t>Log_Sens</t>
+  </si>
+  <si>
+    <t>Log_Spec</t>
+  </si>
+  <si>
+    <t>강남</t>
+  </si>
+  <si>
+    <t>신촌</t>
+  </si>
+  <si>
+    <t>전체</t>
+  </si>
+  <si>
+    <t>Case 1 Clinical</t>
+  </si>
+  <si>
+    <t>Case 2 +AEC_prev</t>
+  </si>
+  <si>
+    <t>Case 3 +AEC_new</t>
+  </si>
+  <si>
+    <t>Case 4 +AEC_prev +Scanner</t>
+  </si>
+  <si>
+    <t>Case 5 +AEC_new +Scanner</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +123,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,622 +439,528 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Hospital</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>N_features</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>N_rows</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Lin_R2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Lin_R2_std</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Lin_MAE</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Lin_RMSE</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>TAMA_threshold</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Log_AUC</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Log_AUC_std</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Log_Acc</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Log_Sens</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Log_Spec</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Case 1 Clinical</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+    <row r="1" spans="1:15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
         <v>1365</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.662</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0.0367</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>12.83</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>17.12</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>100</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>0.8293</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>0.0208</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0.7868000000000001</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>0.3414</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>0.9243</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Case 2 +AEC_prev</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
         <v>7</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>1365</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.678</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>0.0357</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>12.53</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>16.71</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>100</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>0.8346</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>0.0247</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>0.7846</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>0.3447</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>0.9204</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Case 3 +AEC_new</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
         <v>14</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>1365</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.6694</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>0.0385</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>12.59</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>16.93</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>100</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>0.8352000000000001</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>0.0229</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>0.7853</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>0.3571</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>0.9175</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Case 4 +AEC_prev +Scanner</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5">
         <v>46</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>1365</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0.6682</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>0.0318</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>12.77</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>16.96</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>100</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>0.8306</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>0.0209</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>0.7883</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>0.3758</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>0.9156</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Case 5 +AEC_new +Scanner</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6">
         <v>53</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>1365</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0.662</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>0.0353</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>12.74</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>17.11</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>100</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>0.832</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>0.0182</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>0.7941</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>0.3913</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>0.9185</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Case 1 Clinical</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7">
         <v>3</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>1269</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0.6398</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>0.0629</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>13.82</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>18.42</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>103</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>0.8577</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>0.0333</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>0.7999000000000001</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>0.5256</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>0.8901</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Case 2 +AEC_prev</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
         <v>7</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>1269</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>0.6415</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>0.0615</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>13.83</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>18.37</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>103</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>0.8587</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>0.0347</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>0.7983</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>0.5351</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>0.8848</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Case 3 +AEC_new</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
         <v>14</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>1269</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>0.6371</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>0.0673</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>13.81</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>18.48</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>103</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>0.8532999999999999</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>0.0398</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>0.8046</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>0.5413</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9">
         <v>0.8911</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Case 4 +AEC_prev +Scanner</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10">
         <v>59</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1269</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>0.634</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>0.059</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>14</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>18.56</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>103</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>0.8579</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>0.0328</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>0.7943</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>0.5382</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>0.8784999999999999</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>신촌</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Case 5 +AEC_new +Scanner</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11">
         <v>66</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>1269</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>0.6375999999999999</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>0.054</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>13.94</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>18.48</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>103</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>0.8531</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>0.0357</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>0.7943</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>0.5414</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11">
         <v>0.8774999999999999</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/연구코드/results/regression/cross_hospital_summary.xlsx
+++ b/연구코드/results/regression/cross_hospital_summary.xlsx
@@ -528,13 +528,13 @@
         <v>0.0208</v>
       </c>
       <c r="M2">
-        <v>0.7868000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="N2">
-        <v>0.3414</v>
+        <v>0.8754</v>
       </c>
       <c r="O2">
-        <v>0.9243</v>
+        <v>0.6749000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -575,13 +575,13 @@
         <v>0.0247</v>
       </c>
       <c r="M3">
-        <v>0.7846</v>
+        <v>0.7121</v>
       </c>
       <c r="N3">
-        <v>0.3447</v>
+        <v>0.9314</v>
       </c>
       <c r="O3">
-        <v>0.9204</v>
+        <v>0.6443</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -622,13 +622,13 @@
         <v>0.0229</v>
       </c>
       <c r="M4">
-        <v>0.7853</v>
+        <v>0.7201</v>
       </c>
       <c r="N4">
-        <v>0.3571</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="O4">
-        <v>0.9175</v>
+        <v>0.6606</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -669,13 +669,13 @@
         <v>0.0209</v>
       </c>
       <c r="M5">
-        <v>0.7883</v>
+        <v>0.7128</v>
       </c>
       <c r="N5">
-        <v>0.3758</v>
+        <v>0.9035</v>
       </c>
       <c r="O5">
-        <v>0.9156</v>
+        <v>0.6539</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -716,13 +716,13 @@
         <v>0.0182</v>
       </c>
       <c r="M6">
-        <v>0.7941</v>
+        <v>0.7436</v>
       </c>
       <c r="N6">
-        <v>0.3913</v>
+        <v>0.8786</v>
       </c>
       <c r="O6">
-        <v>0.9185</v>
+        <v>0.7018</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -763,13 +763,13 @@
         <v>0.0333</v>
       </c>
       <c r="M7">
-        <v>0.7999000000000001</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="N7">
-        <v>0.5256</v>
+        <v>0.8983</v>
       </c>
       <c r="O7">
-        <v>0.8901</v>
+        <v>0.7246</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -810,13 +810,13 @@
         <v>0.0347</v>
       </c>
       <c r="M8">
-        <v>0.7983</v>
+        <v>0.7841</v>
       </c>
       <c r="N8">
-        <v>0.5351</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="O8">
-        <v>0.8848</v>
+        <v>0.7508</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -857,13 +857,13 @@
         <v>0.0398</v>
       </c>
       <c r="M9">
-        <v>0.8046</v>
+        <v>0.7675</v>
       </c>
       <c r="N9">
-        <v>0.5413</v>
+        <v>0.9015</v>
       </c>
       <c r="O9">
-        <v>0.8911</v>
+        <v>0.7236</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -904,13 +904,13 @@
         <v>0.0328</v>
       </c>
       <c r="M10">
-        <v>0.7943</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="N10">
-        <v>0.5382</v>
+        <v>0.876</v>
       </c>
       <c r="O10">
-        <v>0.8784999999999999</v>
+        <v>0.7654</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -951,13 +951,13 @@
         <v>0.0357</v>
       </c>
       <c r="M11">
-        <v>0.7943</v>
+        <v>0.7833</v>
       </c>
       <c r="N11">
-        <v>0.5414</v>
+        <v>0.9014</v>
       </c>
       <c r="O11">
-        <v>0.8774999999999999</v>
+        <v>0.7445000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/regression/cross_hospital_summary.xlsx
+++ b/연구코드/results/regression/cross_hospital_summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="25">
   <si>
     <t>Hospital</t>
   </si>
@@ -83,6 +83,12 @@
   </si>
   <si>
     <t>Case 5 +AEC_new +Scanner</t>
+  </si>
+  <si>
+    <t>F:95.0/M:132.0</t>
+  </si>
+  <si>
+    <t>F:95.0/M:131.0</t>
   </si>
 </sst>
 </file>
@@ -518,23 +524,23 @@
       <c r="I2">
         <v>17.12</v>
       </c>
-      <c r="J2">
-        <v>100</v>
+      <c r="J2" t="s">
+        <v>23</v>
       </c>
       <c r="K2">
-        <v>0.8293</v>
+        <v>0.7427</v>
       </c>
       <c r="L2">
-        <v>0.0208</v>
+        <v>0.0188</v>
       </c>
       <c r="M2">
-        <v>0.7223000000000001</v>
+        <v>0.6762</v>
       </c>
       <c r="N2">
-        <v>0.8754</v>
+        <v>0.7647</v>
       </c>
       <c r="O2">
-        <v>0.6749000000000001</v>
+        <v>0.6491</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -565,23 +571,23 @@
       <c r="I3">
         <v>16.71</v>
       </c>
-      <c r="J3">
-        <v>100</v>
+      <c r="J3" t="s">
+        <v>23</v>
       </c>
       <c r="K3">
-        <v>0.8346</v>
+        <v>0.751</v>
       </c>
       <c r="L3">
-        <v>0.0247</v>
+        <v>0.0227</v>
       </c>
       <c r="M3">
-        <v>0.7121</v>
+        <v>0.7004</v>
       </c>
       <c r="N3">
-        <v>0.9314</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="O3">
-        <v>0.6443</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -612,23 +618,23 @@
       <c r="I4">
         <v>16.93</v>
       </c>
-      <c r="J4">
-        <v>100</v>
+      <c r="J4" t="s">
+        <v>23</v>
       </c>
       <c r="K4">
-        <v>0.8352000000000001</v>
+        <v>0.7442</v>
       </c>
       <c r="L4">
-        <v>0.0229</v>
+        <v>0.028</v>
       </c>
       <c r="M4">
-        <v>0.7201</v>
+        <v>0.6374</v>
       </c>
       <c r="N4">
-        <v>0.9127999999999999</v>
+        <v>0.8274</v>
       </c>
       <c r="O4">
-        <v>0.6606</v>
+        <v>0.5794</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -659,23 +665,23 @@
       <c r="I5">
         <v>16.96</v>
       </c>
-      <c r="J5">
-        <v>100</v>
+      <c r="J5" t="s">
+        <v>23</v>
       </c>
       <c r="K5">
-        <v>0.8306</v>
+        <v>0.74</v>
       </c>
       <c r="L5">
-        <v>0.0209</v>
+        <v>0.0287</v>
       </c>
       <c r="M5">
-        <v>0.7128</v>
+        <v>0.6674</v>
       </c>
       <c r="N5">
-        <v>0.9035</v>
+        <v>0.7834</v>
       </c>
       <c r="O5">
-        <v>0.6539</v>
+        <v>0.6319</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -706,23 +712,23 @@
       <c r="I6">
         <v>17.11</v>
       </c>
-      <c r="J6">
-        <v>100</v>
+      <c r="J6" t="s">
+        <v>23</v>
       </c>
       <c r="K6">
-        <v>0.832</v>
+        <v>0.7311</v>
       </c>
       <c r="L6">
-        <v>0.0182</v>
+        <v>0.0291</v>
       </c>
       <c r="M6">
-        <v>0.7436</v>
+        <v>0.6762</v>
       </c>
       <c r="N6">
-        <v>0.8786</v>
+        <v>0.7522</v>
       </c>
       <c r="O6">
-        <v>0.7018</v>
+        <v>0.6529</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -753,23 +759,23 @@
       <c r="I7">
         <v>18.42</v>
       </c>
-      <c r="J7">
-        <v>103</v>
+      <c r="J7" t="s">
+        <v>24</v>
       </c>
       <c r="K7">
-        <v>0.8577</v>
+        <v>0.7513</v>
       </c>
       <c r="L7">
-        <v>0.0333</v>
+        <v>0.0332</v>
       </c>
       <c r="M7">
-        <v>0.7675999999999999</v>
+        <v>0.6541</v>
       </c>
       <c r="N7">
-        <v>0.8983</v>
+        <v>0.7988</v>
       </c>
       <c r="O7">
-        <v>0.7246</v>
+        <v>0.6073</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -800,23 +806,23 @@
       <c r="I8">
         <v>18.37</v>
       </c>
-      <c r="J8">
-        <v>103</v>
+      <c r="J8" t="s">
+        <v>24</v>
       </c>
       <c r="K8">
-        <v>0.8587</v>
+        <v>0.7502</v>
       </c>
       <c r="L8">
-        <v>0.0347</v>
+        <v>0.0362</v>
       </c>
       <c r="M8">
-        <v>0.7841</v>
+        <v>0.6596</v>
       </c>
       <c r="N8">
-        <v>0.8856000000000001</v>
+        <v>0.8055</v>
       </c>
       <c r="O8">
-        <v>0.7508</v>
+        <v>0.6125</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -847,23 +853,23 @@
       <c r="I9">
         <v>18.48</v>
       </c>
-      <c r="J9">
-        <v>103</v>
+      <c r="J9" t="s">
+        <v>24</v>
       </c>
       <c r="K9">
-        <v>0.8532999999999999</v>
+        <v>0.7492</v>
       </c>
       <c r="L9">
-        <v>0.0398</v>
+        <v>0.0239</v>
       </c>
       <c r="M9">
-        <v>0.7675</v>
+        <v>0.6762</v>
       </c>
       <c r="N9">
-        <v>0.9015</v>
+        <v>0.7857</v>
       </c>
       <c r="O9">
-        <v>0.7236</v>
+        <v>0.6405999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -894,23 +900,23 @@
       <c r="I10">
         <v>18.56</v>
       </c>
-      <c r="J10">
-        <v>103</v>
+      <c r="J10" t="s">
+        <v>24</v>
       </c>
       <c r="K10">
-        <v>0.8579</v>
+        <v>0.7529</v>
       </c>
       <c r="L10">
-        <v>0.0328</v>
+        <v>0.0321</v>
       </c>
       <c r="M10">
-        <v>0.7927999999999999</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="N10">
-        <v>0.876</v>
+        <v>0.7572</v>
       </c>
       <c r="O10">
-        <v>0.7654</v>
+        <v>0.6896</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -941,23 +947,23 @@
       <c r="I11">
         <v>18.48</v>
       </c>
-      <c r="J11">
-        <v>103</v>
+      <c r="J11" t="s">
+        <v>24</v>
       </c>
       <c r="K11">
-        <v>0.8531</v>
+        <v>0.7493</v>
       </c>
       <c r="L11">
-        <v>0.0357</v>
+        <v>0.0342</v>
       </c>
       <c r="M11">
-        <v>0.7833</v>
+        <v>0.7164</v>
       </c>
       <c r="N11">
-        <v>0.9014</v>
+        <v>0.6987</v>
       </c>
       <c r="O11">
-        <v>0.7445000000000001</v>
+        <v>0.7219</v>
       </c>
     </row>
   </sheetData>
